--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF1073E-B2FF-4B6F-8DCF-A080231A98D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2466FAE-9BC0-40E9-BE54-7B6F54FD5A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="45" windowWidth="20355" windowHeight="10920" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
@@ -395,10 +395,10 @@
     <t>patrick.m1@yopmail.com</t>
   </si>
   <si>
-    <t>fieldAcknowledgement__c</t>
-  </si>
-  <si>
     <t>Checked</t>
+  </si>
+  <si>
+    <t>Acknowledgement__c</t>
   </si>
 </sst>
 </file>
@@ -736,14 +736,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,7 +754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -765,7 +765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -776,7 +776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -787,7 +787,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -798,7 +798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -809,7 +809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -820,7 +820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -831,7 +831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -842,7 +842,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -853,7 +853,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -864,7 +864,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -875,7 +875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -886,7 +886,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -897,7 +897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -908,7 +908,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -919,7 +919,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -939,14 +939,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E933553B-F95A-4F01-B650-F128024556A7}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -957,7 +957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -968,7 +968,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -979,7 +979,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -990,7 +990,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1243,15 +1243,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>3</v>
       </c>
       <c r="B28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
         <v>120</v>
-      </c>
-      <c r="C28" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1263,14 +1263,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D567C1-3DF3-4A2F-81EA-BD233AA6E8B9}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1576,14 +1576,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C1E5FC-A472-4829-80F3-B98167454D1D}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1880,15 +1880,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>3</v>
       </c>
       <c r="B28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
         <v>120</v>
-      </c>
-      <c r="C28" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1899,14 +1899,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCCECC7-00A8-4B5C-8E26-F12B19BBAB15}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2135,14 +2135,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F1390A-D12F-4F18-A1BB-7ED029060CF4}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2370,13 +2370,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F0F804-2965-4582-8FDA-ADDB9C543F42}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>109</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>109</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>109</v>
       </c>
@@ -2454,14 +2454,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884CED2-BC36-4C90-AFF4-891CB304FFFD}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2690,14 +2690,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F9EB-A64B-4606-8898-C4C711484B16}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2466FAE-9BC0-40E9-BE54-7B6F54FD5A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4FACF5-39F2-4B57-A3EF-8DD44E9253E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="122">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -736,14 +736,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,7 +754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -765,7 +765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -776,7 +776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -787,7 +787,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -798,7 +798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -809,7 +809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -820,7 +820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -831,7 +831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -842,7 +842,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -853,7 +853,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -864,7 +864,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -875,7 +875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -886,7 +886,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -897,7 +897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -908,7 +908,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -919,7 +919,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -939,14 +939,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E933553B-F95A-4F01-B650-F128024556A7}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.81640625" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -957,7 +957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -968,7 +968,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -979,7 +979,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -990,7 +990,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1262,15 +1262,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D567C1-3DF3-4A2F-81EA-BD233AA6E8B9}">
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1565,6 +1565,17 @@
       </c>
       <c r="C27" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1576,14 +1587,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C1E5FC-A472-4829-80F3-B98167454D1D}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1594,7 +1605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1605,7 +1616,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1616,7 +1627,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1627,7 +1638,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1638,7 +1649,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1649,7 +1660,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1660,7 +1671,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1671,7 +1682,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1682,7 +1693,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1693,7 +1704,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1704,7 +1715,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1715,7 +1726,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1726,7 +1737,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1737,7 +1748,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1748,7 +1759,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1759,7 +1770,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1770,7 +1781,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1781,7 +1792,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1792,7 +1803,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1803,7 +1814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1814,7 +1825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1825,7 +1836,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1836,7 +1847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1847,7 +1858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1858,7 +1869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1869,7 +1880,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1880,7 +1891,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1899,14 +1910,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCCECC7-00A8-4B5C-8E26-F12B19BBAB15}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1917,7 +1928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1928,7 +1939,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1939,7 +1950,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1950,7 +1961,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1961,7 +1972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1972,7 +1983,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1983,7 +1994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1994,7 +2005,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2005,7 +2016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2016,7 +2027,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2027,7 +2038,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2038,7 +2049,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2049,7 +2060,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2060,7 +2071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2071,7 +2082,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2082,7 +2093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2093,7 +2104,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2104,7 +2115,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2115,7 +2126,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2135,14 +2146,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F1390A-D12F-4F18-A1BB-7ED029060CF4}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2153,7 +2164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2164,7 +2175,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2175,7 +2186,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2186,7 +2197,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2197,7 +2208,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2208,7 +2219,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2219,7 +2230,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2230,7 +2241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2241,7 +2252,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2252,7 +2263,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2263,7 +2274,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2274,7 +2285,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2285,7 +2296,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2296,7 +2307,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2307,7 +2318,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2318,7 +2329,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2329,7 +2340,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2340,7 +2351,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2351,7 +2362,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2370,13 +2381,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F0F804-2965-4582-8FDA-ADDB9C543F42}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2387,7 +2398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
@@ -2398,7 +2409,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>109</v>
       </c>
@@ -2409,7 +2420,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>109</v>
       </c>
@@ -2420,7 +2431,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
@@ -2431,7 +2442,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>109</v>
       </c>
@@ -2454,14 +2465,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884CED2-BC36-4C90-AFF4-891CB304FFFD}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2472,7 +2483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2483,7 +2494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2494,7 +2505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2505,7 +2516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2516,7 +2527,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2527,7 +2538,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2538,7 +2549,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2549,7 +2560,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2560,7 +2571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2571,7 +2582,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2582,7 +2593,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2593,7 +2604,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2604,7 +2615,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2615,7 +2626,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2626,7 +2637,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2637,7 +2648,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2648,7 +2659,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2659,7 +2670,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2670,7 +2681,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2690,14 +2701,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F9EB-A64B-4606-8898-C4C711484B16}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2708,7 +2719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2719,7 +2730,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2730,7 +2741,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2741,7 +2752,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2752,7 +2763,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2763,7 +2774,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2774,7 +2785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2785,7 +2796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2796,7 +2807,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2807,7 +2818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2818,7 +2829,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2829,7 +2840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2840,7 +2851,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2851,7 +2862,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2862,7 +2873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2873,7 +2884,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2884,7 +2895,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2895,7 +2906,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/RiskAssessment_Field_Values.xlsx
+++ b/src/main/resources/RiskAssessment_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Va Qa Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4FACF5-39F2-4B57-A3EF-8DD44E9253E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1F647B-2715-4A76-9DDC-9EAEC341D066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RiskAssessmentValues2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="125">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -399,6 +399,15 @@
   </si>
   <si>
     <t>Acknowledgement__c</t>
+  </si>
+  <si>
+    <t>This Award does not have a match requirement</t>
+  </si>
+  <si>
+    <t>No personnel on Award</t>
+  </si>
+  <si>
+    <t>Not Applicable - N/A (for new Grantee)</t>
   </si>
 </sst>
 </file>
@@ -2546,7 +2555,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2612,7 +2621,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2623,7 +2632,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2667,7 +2676,7 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2678,7 +2687,7 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2689,7 +2698,7 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
